--- a/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
+++ b/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
@@ -1304,17 +1304,9 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1796010</t>
-        </is>
-      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1796010</t>
-        </is>
-      </c>
+      <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="6" t="inlineStr">

--- a/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
+++ b/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
@@ -1324,7 +1324,7 @@
         <v>15</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
@@ -1386,31 +1386,63 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
+      <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
+      <c r="J8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
+      <c r="O8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="R8" s="6" t="n"/>
       <c r="S8" s="6" t="n"/>
       <c r="T8" s="6" t="n"/>
       <c r="U8" s="6" t="n"/>
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
-      <c r="X8" s="6" t="n"/>
-      <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
+      <c r="X8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z8" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA8" s="6" t="n"/>
       <c r="AB8" s="6" t="n"/>
       <c r="AC8" s="6" t="n"/>
@@ -1436,31 +1468,63 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
+      <c r="J9" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
-      <c r="O9" s="6" t="n"/>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n"/>
+      <c r="O9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="R9" s="6" t="n"/>
       <c r="S9" s="6" t="n"/>
       <c r="T9" s="6" t="n"/>
       <c r="U9" s="6" t="n"/>
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
-      <c r="X9" s="6" t="n"/>
-      <c r="Y9" s="6" t="n"/>
-      <c r="Z9" s="6" t="n"/>
+      <c r="X9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA9" s="6" t="n"/>
       <c r="AB9" s="6" t="n"/>
       <c r="AC9" s="6" t="n"/>
@@ -1486,31 +1550,63 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
+      <c r="D10" s="5" t="inlineStr"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="J10" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
-      <c r="O10" s="6" t="n"/>
-      <c r="P10" s="6" t="n"/>
-      <c r="Q10" s="6" t="n"/>
+      <c r="O10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="R10" s="6" t="n"/>
       <c r="S10" s="6" t="n"/>
       <c r="T10" s="6" t="n"/>
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
-      <c r="X10" s="6" t="n"/>
-      <c r="Y10" s="6" t="n"/>
-      <c r="Z10" s="6" t="n"/>
+      <c r="X10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA10" s="6" t="n"/>
       <c r="AB10" s="6" t="n"/>
       <c r="AC10" s="6" t="n"/>
@@ -1536,31 +1632,63 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
+      <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
+      <c r="J11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="6" t="n"/>
-      <c r="P11" s="6" t="n"/>
-      <c r="Q11" s="6" t="n"/>
+      <c r="O11" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R11" s="6" t="n"/>
       <c r="S11" s="6" t="n"/>
       <c r="T11" s="6" t="n"/>
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
+      <c r="X11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
@@ -1586,31 +1714,63 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
+      <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="J12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="6" t="n"/>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
+      <c r="O12" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R12" s="6" t="n"/>
       <c r="S12" s="6" t="n"/>
       <c r="T12" s="6" t="n"/>
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
+      <c r="X12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
@@ -1636,31 +1796,63 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
+      <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="J13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="6" t="n"/>
-      <c r="P13" s="6" t="n"/>
-      <c r="Q13" s="6" t="n"/>
+      <c r="O13" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R13" s="6" t="n"/>
       <c r="S13" s="6" t="n"/>
       <c r="T13" s="6" t="n"/>
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
@@ -1686,31 +1878,63 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="5" t="inlineStr"/>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
+      <c r="J14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="6" t="n"/>
-      <c r="P14" s="6" t="n"/>
-      <c r="Q14" s="6" t="n"/>
+      <c r="O14" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R14" s="6" t="n"/>
       <c r="S14" s="6" t="n"/>
       <c r="T14" s="6" t="n"/>
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
@@ -1736,31 +1960,63 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="n"/>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
+      <c r="J15" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="6" t="n"/>
-      <c r="P15" s="6" t="n"/>
-      <c r="Q15" s="6" t="n"/>
+      <c r="O15" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R15" s="6" t="n"/>
       <c r="S15" s="6" t="n"/>
       <c r="T15" s="6" t="n"/>
       <c r="U15" s="6" t="n"/>
       <c r="V15" s="6" t="n"/>
       <c r="W15" s="6" t="n"/>
-      <c r="X15" s="6" t="n"/>
-      <c r="Y15" s="6" t="n"/>
-      <c r="Z15" s="6" t="n"/>
+      <c r="X15" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y15" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z15" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA15" s="6" t="n"/>
       <c r="AB15" s="6" t="n"/>
       <c r="AC15" s="6" t="n"/>
@@ -1786,31 +2042,63 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
+      <c r="D16" s="5" t="inlineStr"/>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="6" t="n"/>
+      <c r="J16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="6" t="n"/>
-      <c r="P16" s="6" t="n"/>
-      <c r="Q16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R16" s="6" t="n"/>
       <c r="S16" s="6" t="n"/>
       <c r="T16" s="6" t="n"/>
       <c r="U16" s="6" t="n"/>
       <c r="V16" s="6" t="n"/>
       <c r="W16" s="6" t="n"/>
-      <c r="X16" s="6" t="n"/>
-      <c r="Y16" s="6" t="n"/>
-      <c r="Z16" s="6" t="n"/>
+      <c r="X16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Y16" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z16" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA16" s="6" t="n"/>
       <c r="AB16" s="6" t="n"/>
       <c r="AC16" s="6" t="n"/>
@@ -1836,31 +2124,63 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
+      <c r="D17" s="5" t="inlineStr"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="6" t="n"/>
+      <c r="J17" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="6" t="n"/>
-      <c r="P17" s="6" t="n"/>
-      <c r="Q17" s="6" t="n"/>
+      <c r="O17" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R17" s="6" t="n"/>
       <c r="S17" s="6" t="n"/>
       <c r="T17" s="6" t="n"/>
       <c r="U17" s="6" t="n"/>
       <c r="V17" s="6" t="n"/>
       <c r="W17" s="6" t="n"/>
-      <c r="X17" s="6" t="n"/>
-      <c r="Y17" s="6" t="n"/>
-      <c r="Z17" s="6" t="n"/>
+      <c r="X17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA17" s="6" t="n"/>
       <c r="AB17" s="6" t="n"/>
       <c r="AC17" s="6" t="n"/>
@@ -1886,31 +2206,63 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
+      <c r="D18" s="5" t="inlineStr"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="6" t="n"/>
+      <c r="J18" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="6" t="n"/>
-      <c r="P18" s="6" t="n"/>
-      <c r="Q18" s="6" t="n"/>
+      <c r="O18" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R18" s="6" t="n"/>
       <c r="S18" s="6" t="n"/>
       <c r="T18" s="6" t="n"/>
       <c r="U18" s="6" t="n"/>
       <c r="V18" s="6" t="n"/>
       <c r="W18" s="6" t="n"/>
-      <c r="X18" s="6" t="n"/>
-      <c r="Y18" s="6" t="n"/>
-      <c r="Z18" s="6" t="n"/>
+      <c r="X18" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y18" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z18" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA18" s="6" t="n"/>
       <c r="AB18" s="6" t="n"/>
       <c r="AC18" s="6" t="n"/>
@@ -1936,31 +2288,63 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr"/>
       <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
+      <c r="D19" s="5" t="inlineStr"/>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="J19" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="6" t="n"/>
-      <c r="P19" s="6" t="n"/>
-      <c r="Q19" s="6" t="n"/>
+      <c r="O19" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R19" s="6" t="n"/>
       <c r="S19" s="6" t="n"/>
       <c r="T19" s="6" t="n"/>
       <c r="U19" s="6" t="n"/>
       <c r="V19" s="6" t="n"/>
       <c r="W19" s="6" t="n"/>
-      <c r="X19" s="6" t="n"/>
-      <c r="Y19" s="6" t="n"/>
-      <c r="Z19" s="6" t="n"/>
+      <c r="X19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z19" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA19" s="6" t="n"/>
       <c r="AB19" s="6" t="n"/>
       <c r="AC19" s="6" t="n"/>
@@ -1986,31 +2370,63 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="D20" s="5" t="inlineStr"/>
       <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="J20" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n"/>
+      <c r="O20" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R20" s="6" t="n"/>
       <c r="S20" s="6" t="n"/>
       <c r="T20" s="6" t="n"/>
       <c r="U20" s="6" t="n"/>
       <c r="V20" s="6" t="n"/>
       <c r="W20" s="6" t="n"/>
-      <c r="X20" s="6" t="n"/>
-      <c r="Y20" s="6" t="n"/>
-      <c r="Z20" s="6" t="n"/>
+      <c r="X20" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y20" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z20" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA20" s="6" t="n"/>
       <c r="AB20" s="6" t="n"/>
       <c r="AC20" s="6" t="n"/>
@@ -2036,31 +2452,63 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
+      <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
+      <c r="J21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
+      <c r="O21" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R21" s="6" t="n"/>
       <c r="S21" s="6" t="n"/>
       <c r="T21" s="6" t="n"/>
       <c r="U21" s="6" t="n"/>
       <c r="V21" s="6" t="n"/>
       <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
+      <c r="X21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z21" s="6" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="AA21" s="6" t="n"/>
       <c r="AB21" s="6" t="n"/>
       <c r="AC21" s="6" t="n"/>
@@ -2086,31 +2534,63 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr"/>
       <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
+      <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
+      <c r="J22" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
+      <c r="O22" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="R22" s="6" t="n"/>
       <c r="S22" s="6" t="n"/>
       <c r="T22" s="6" t="n"/>
       <c r="U22" s="6" t="n"/>
       <c r="V22" s="6" t="n"/>
       <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
+      <c r="X22" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y22" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z22" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA22" s="6" t="n"/>
       <c r="AB22" s="6" t="n"/>
       <c r="AC22" s="6" t="n"/>

--- a/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
+++ b/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
@@ -1304,11 +1304,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1386,11 +1406,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1468,11 +1508,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1550,11 +1610,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1632,11 +1712,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1714,11 +1814,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1796,11 +1916,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1878,11 +2018,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -1960,11 +2120,31 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
-      <c r="B15" s="5" t="inlineStr"/>
-      <c r="C15" s="5" t="n"/>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2042,11 +2222,31 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
-      <c r="B16" s="5" t="inlineStr"/>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2124,11 +2324,31 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2206,11 +2426,31 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
-      <c r="B18" s="5" t="inlineStr"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2288,11 +2528,31 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
-      <c r="B19" s="5" t="inlineStr"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2370,11 +2630,31 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="inlineStr"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2452,11 +2732,31 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
-      <c r="B21" s="5" t="inlineStr"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2534,11 +2834,31 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
-      <c r="B22" s="5" t="inlineStr"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>1796010</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>179610</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 Wealth단체저축보험 무배당</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>S00026</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
+++ b/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>179610</t>
+          <t>1796010</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">

--- a/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
+++ b/output/upload/S00026_1796_Wealth단체저축보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
